--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_016.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_016.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1876" uniqueCount="184">
   <si>
     <t>Sezione</t>
   </si>
@@ -278,99 +278,108 @@
     <t>residenzaOriginaria</t>
   </si>
   <si>
+    <t>Genitore</t>
+  </si>
+  <si>
+    <t>evento.madre</t>
+  </si>
+  <si>
+    <t>evento.flagOmogenitoriale,=,false</t>
+  </si>
+  <si>
+    <t>Stato di nascita</t>
+  </si>
+  <si>
+    <t>Stato di nascita - Descrizione</t>
+  </si>
+  <si>
+    <t>Provincia di nascita</t>
+  </si>
+  <si>
+    <t>Provincia di nascita - Descrizione</t>
+  </si>
+  <si>
+    <t>Comune di nascita</t>
+  </si>
+  <si>
+    <t>Comune di nascita - Descrizione</t>
+  </si>
+  <si>
+    <t>Nazionalità - Descrizione</t>
+  </si>
+  <si>
+    <t>Comprensione</t>
+  </si>
+  <si>
+    <t>tipoImpedimento</t>
+  </si>
+  <si>
+    <t>Stato di residenza</t>
+  </si>
+  <si>
+    <t>Stato di residenza - Descrizione</t>
+  </si>
+  <si>
+    <t>Provincia di residenza</t>
+  </si>
+  <si>
+    <t>Provincia di residenza - Descrizione</t>
+  </si>
+  <si>
+    <t>Comune di residenza</t>
+  </si>
+  <si>
+    <t>Comune di residenza - Descrizione</t>
+  </si>
+  <si>
+    <t>Indirizzo di residenza</t>
+  </si>
+  <si>
+    <t>flag dichiarante</t>
+  </si>
+  <si>
+    <t>flagDichiarante</t>
+  </si>
+  <si>
+    <t>flag comparente</t>
+  </si>
+  <si>
+    <t>flagComparente</t>
+  </si>
+  <si>
+    <t>flag firmatario</t>
+  </si>
+  <si>
+    <t>flagFirmatario</t>
+  </si>
+  <si>
+    <t>Trasmissione residenza estera</t>
+  </si>
+  <si>
+    <t>flagTrasmissioneResidenzaEstera</t>
+  </si>
+  <si>
     <t>Madre</t>
   </si>
   <si>
-    <t>evento.madre</t>
+    <t>evento.flagOmogenitoriale,=,true</t>
+  </si>
+  <si>
+    <t>evento.padre</t>
+  </si>
+  <si>
+    <t>Padre</t>
+  </si>
+  <si>
+    <t>Madre biologica</t>
+  </si>
+  <si>
+    <t>evento.madreBiologica</t>
   </si>
   <si>
     <t>opzionale</t>
   </si>
   <si>
-    <t>Stato di nascita</t>
-  </si>
-  <si>
-    <t>Stato di nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>Provincia di nascita</t>
-  </si>
-  <si>
-    <t>Provincia di nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>Comune di nascita</t>
-  </si>
-  <si>
-    <t>Comune di nascita - Descrizione</t>
-  </si>
-  <si>
-    <t>Nazionalità - Descrizione</t>
-  </si>
-  <si>
-    <t>Comprensione</t>
-  </si>
-  <si>
-    <t>tipoImpedimento</t>
-  </si>
-  <si>
-    <t>Stato di residenza</t>
-  </si>
-  <si>
-    <t>Stato di residenza - Descrizione</t>
-  </si>
-  <si>
-    <t>Provincia di residenza</t>
-  </si>
-  <si>
-    <t>Provincia di residenza - Descrizione</t>
-  </si>
-  <si>
-    <t>Comune di residenza</t>
-  </si>
-  <si>
-    <t>Comune di residenza - Descrizione</t>
-  </si>
-  <si>
-    <t>Indirizzo di residenza</t>
-  </si>
-  <si>
-    <t>flag dichiarante</t>
-  </si>
-  <si>
-    <t>flagDichiarante</t>
-  </si>
-  <si>
-    <t>flag comparente</t>
-  </si>
-  <si>
-    <t>flagComparente</t>
-  </si>
-  <si>
-    <t>flag firmatario</t>
-  </si>
-  <si>
-    <t>flagFirmatario</t>
-  </si>
-  <si>
-    <t>Trasmissione residenza estera</t>
-  </si>
-  <si>
-    <t>flagTrasmissioneResidenzaEstera</t>
-  </si>
-  <si>
-    <t>Padre</t>
-  </si>
-  <si>
-    <t>evento.padre</t>
-  </si>
-  <si>
-    <t>Madre biologica</t>
-  </si>
-  <si>
-    <t>evento.madreBiologica</t>
-  </si>
-  <si>
     <t>Padre biologico</t>
   </si>
   <si>
@@ -546,6 +555,15 @@
   </si>
   <si>
     <t>testoLibero</t>
+  </si>
+  <si>
+    <t>Dettagli evento</t>
+  </si>
+  <si>
+    <t>Adozione omogenitoriale</t>
+  </si>
+  <si>
+    <t>flagOmogenitoriale</t>
   </si>
 </sst>
 </file>
@@ -604,7 +622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H201"/>
+  <dimension ref="A1:H268"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.59765625" customWidth="true" bestFit="true"/>
@@ -613,7 +631,7 @@
     <col min="4" max="4" width="40.45703125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="28.44921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="31.45703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2260,7 +2278,7 @@
         <v>27</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>29</v>
@@ -2269,7 +2287,7 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="73">
@@ -2283,7 +2301,7 @@
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>31</v>
@@ -2292,7 +2310,7 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74">
@@ -2306,7 +2324,7 @@
         <v>27</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>35</v>
@@ -2315,7 +2333,7 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75">
@@ -2329,7 +2347,7 @@
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>37</v>
@@ -2338,7 +2356,7 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76">
@@ -2352,7 +2370,7 @@
         <v>27</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>39</v>
@@ -2361,7 +2379,7 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77">
@@ -2375,7 +2393,7 @@
         <v>27</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>41</v>
@@ -2384,7 +2402,7 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78">
@@ -2398,7 +2416,7 @@
         <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>43</v>
@@ -2407,7 +2425,7 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79">
@@ -2421,7 +2439,7 @@
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>45</v>
@@ -2430,7 +2448,7 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80">
@@ -2444,7 +2462,7 @@
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>47</v>
@@ -2453,7 +2471,7 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81">
@@ -2467,7 +2485,7 @@
         <v>27</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>49</v>
@@ -2476,7 +2494,7 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82">
@@ -2490,7 +2508,7 @@
         <v>27</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>51</v>
@@ -2499,7 +2517,7 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83">
@@ -2513,7 +2531,7 @@
         <v>27</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>53</v>
@@ -2522,7 +2540,7 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84">
@@ -2536,7 +2554,7 @@
         <v>27</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>55</v>
@@ -2545,7 +2563,7 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85">
@@ -2559,7 +2577,7 @@
         <v>27</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>57</v>
@@ -2568,7 +2586,7 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86">
@@ -2582,7 +2600,7 @@
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>59</v>
@@ -2591,7 +2609,7 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87">
@@ -2605,7 +2623,7 @@
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>61</v>
@@ -2614,7 +2632,7 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88">
@@ -2628,7 +2646,7 @@
         <v>27</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>99</v>
@@ -2637,7 +2655,7 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89">
@@ -2651,7 +2669,7 @@
         <v>27</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>63</v>
@@ -2660,7 +2678,7 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90">
@@ -2674,7 +2692,7 @@
         <v>27</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>65</v>
@@ -2683,7 +2701,7 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91">
@@ -2697,7 +2715,7 @@
         <v>27</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>67</v>
@@ -2706,7 +2724,7 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92">
@@ -2720,7 +2738,7 @@
         <v>27</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>69</v>
@@ -2729,7 +2747,7 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93">
@@ -2743,7 +2761,7 @@
         <v>27</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>71</v>
@@ -2752,7 +2770,7 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94">
@@ -2766,7 +2784,7 @@
         <v>27</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>73</v>
@@ -2775,7 +2793,7 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95">
@@ -2789,7 +2807,7 @@
         <v>27</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>75</v>
@@ -2798,7 +2816,7 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96">
@@ -2812,7 +2830,7 @@
         <v>27</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>77</v>
@@ -2821,7 +2839,7 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97">
@@ -2835,7 +2853,7 @@
         <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>108</v>
@@ -2844,7 +2862,7 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98">
@@ -2858,7 +2876,7 @@
         <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>110</v>
@@ -2867,7 +2885,7 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="99">
@@ -2881,7 +2899,7 @@
         <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>112</v>
@@ -2890,7 +2908,7 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100">
@@ -2904,7 +2922,7 @@
         <v>27</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>79</v>
@@ -2913,7 +2931,7 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101">
@@ -2927,7 +2945,7 @@
         <v>27</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>81</v>
@@ -2936,7 +2954,7 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="102">
@@ -2950,7 +2968,7 @@
         <v>27</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>83</v>
@@ -2959,7 +2977,7 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="103">
@@ -2973,7 +2991,7 @@
         <v>27</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>85</v>
@@ -2982,7 +3000,7 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="104">
@@ -2996,7 +3014,7 @@
         <v>27</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>114</v>
@@ -3005,12 +3023,12 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>26</v>
@@ -3019,7 +3037,7 @@
         <v>27</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>29</v>
@@ -3033,7 +3051,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>30</v>
@@ -3042,7 +3060,7 @@
         <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>31</v>
@@ -3056,7 +3074,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>34</v>
@@ -3065,7 +3083,7 @@
         <v>27</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>35</v>
@@ -3079,7 +3097,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>36</v>
@@ -3088,7 +3106,7 @@
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>37</v>
@@ -3102,7 +3120,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>38</v>
@@ -3111,7 +3129,7 @@
         <v>27</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>39</v>
@@ -3125,7 +3143,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>40</v>
@@ -3134,7 +3152,7 @@
         <v>27</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>41</v>
@@ -3148,7 +3166,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>42</v>
@@ -3157,7 +3175,7 @@
         <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>43</v>
@@ -3171,7 +3189,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>91</v>
@@ -3180,7 +3198,7 @@
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>45</v>
@@ -3194,7 +3212,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>92</v>
@@ -3203,7 +3221,7 @@
         <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>47</v>
@@ -3217,7 +3235,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>93</v>
@@ -3226,7 +3244,7 @@
         <v>27</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>49</v>
@@ -3240,7 +3258,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>94</v>
@@ -3249,7 +3267,7 @@
         <v>27</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>51</v>
@@ -3263,7 +3281,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>95</v>
@@ -3272,7 +3290,7 @@
         <v>27</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>53</v>
@@ -3286,7 +3304,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>96</v>
@@ -3295,7 +3313,7 @@
         <v>27</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>55</v>
@@ -3309,7 +3327,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>56</v>
@@ -3318,7 +3336,7 @@
         <v>27</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>57</v>
@@ -3332,7 +3350,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>58</v>
@@ -3341,7 +3359,7 @@
         <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>59</v>
@@ -3355,7 +3373,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>97</v>
@@ -3364,7 +3382,7 @@
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>61</v>
@@ -3378,7 +3396,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>98</v>
@@ -3387,7 +3405,7 @@
         <v>27</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>99</v>
@@ -3401,7 +3419,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>62</v>
@@ -3410,7 +3428,7 @@
         <v>27</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>63</v>
@@ -3424,7 +3442,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>100</v>
@@ -3433,7 +3451,7 @@
         <v>27</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>65</v>
@@ -3447,7 +3465,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>101</v>
@@ -3456,7 +3474,7 @@
         <v>27</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>67</v>
@@ -3470,7 +3488,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>102</v>
@@ -3479,7 +3497,7 @@
         <v>27</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>69</v>
@@ -3493,7 +3511,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>103</v>
@@ -3502,7 +3520,7 @@
         <v>27</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>71</v>
@@ -3516,7 +3534,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>104</v>
@@ -3525,7 +3543,7 @@
         <v>27</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>73</v>
@@ -3539,7 +3557,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>105</v>
@@ -3548,7 +3566,7 @@
         <v>27</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>75</v>
@@ -3562,7 +3580,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>106</v>
@@ -3571,7 +3589,7 @@
         <v>27</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>77</v>
@@ -3585,7 +3603,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>107</v>
@@ -3594,7 +3612,7 @@
         <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>108</v>
@@ -3608,7 +3626,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>109</v>
@@ -3617,7 +3635,7 @@
         <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>110</v>
@@ -3631,7 +3649,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>111</v>
@@ -3640,7 +3658,7 @@
         <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>112</v>
@@ -3654,7 +3672,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>78</v>
@@ -3663,7 +3681,7 @@
         <v>27</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>79</v>
@@ -3677,7 +3695,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>80</v>
@@ -3686,7 +3704,7 @@
         <v>27</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>81</v>
@@ -3700,7 +3718,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>82</v>
@@ -3709,7 +3727,7 @@
         <v>27</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>83</v>
@@ -3723,7 +3741,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>84</v>
@@ -3732,7 +3750,7 @@
         <v>27</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>85</v>
@@ -3746,7 +3764,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>113</v>
@@ -3755,7 +3773,7 @@
         <v>27</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>114</v>
@@ -3769,7 +3787,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>26</v>
@@ -3778,7 +3796,7 @@
         <v>27</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>29</v>
@@ -3787,12 +3805,12 @@
         <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>30</v>
@@ -3801,7 +3819,7 @@
         <v>9</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>31</v>
@@ -3810,12 +3828,12 @@
         <v>10</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>34</v>
@@ -3824,7 +3842,7 @@
         <v>27</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>35</v>
@@ -3833,12 +3851,12 @@
         <v>10</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>36</v>
@@ -3847,7 +3865,7 @@
         <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>37</v>
@@ -3856,12 +3874,12 @@
         <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>38</v>
@@ -3870,7 +3888,7 @@
         <v>27</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>39</v>
@@ -3879,12 +3897,12 @@
         <v>10</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>40</v>
@@ -3893,7 +3911,7 @@
         <v>27</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>41</v>
@@ -3902,12 +3920,12 @@
         <v>10</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>42</v>
@@ -3916,7 +3934,7 @@
         <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>43</v>
@@ -3925,12 +3943,12 @@
         <v>10</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>91</v>
@@ -3939,7 +3957,7 @@
         <v>9</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>45</v>
@@ -3948,12 +3966,12 @@
         <v>10</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>92</v>
@@ -3962,7 +3980,7 @@
         <v>9</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>47</v>
@@ -3971,12 +3989,12 @@
         <v>10</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>93</v>
@@ -3985,7 +4003,7 @@
         <v>27</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>49</v>
@@ -3994,12 +4012,12 @@
         <v>10</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>94</v>
@@ -4008,7 +4026,7 @@
         <v>27</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>51</v>
@@ -4017,12 +4035,12 @@
         <v>10</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>95</v>
@@ -4031,7 +4049,7 @@
         <v>27</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>53</v>
@@ -4040,12 +4058,12 @@
         <v>10</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>96</v>
@@ -4054,7 +4072,7 @@
         <v>27</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>55</v>
@@ -4063,12 +4081,12 @@
         <v>10</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>56</v>
@@ -4077,7 +4095,7 @@
         <v>27</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>57</v>
@@ -4086,12 +4104,12 @@
         <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>58</v>
@@ -4100,7 +4118,7 @@
         <v>9</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>59</v>
@@ -4109,12 +4127,12 @@
         <v>10</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>97</v>
@@ -4123,7 +4141,7 @@
         <v>9</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>61</v>
@@ -4132,12 +4150,12 @@
         <v>10</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>98</v>
@@ -4146,7 +4164,7 @@
         <v>27</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>99</v>
@@ -4155,12 +4173,12 @@
         <v>10</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>62</v>
@@ -4169,7 +4187,7 @@
         <v>27</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>63</v>
@@ -4178,12 +4196,12 @@
         <v>10</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>100</v>
@@ -4192,7 +4210,7 @@
         <v>27</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>65</v>
@@ -4201,12 +4219,12 @@
         <v>10</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>101</v>
@@ -4215,7 +4233,7 @@
         <v>27</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>67</v>
@@ -4224,12 +4242,12 @@
         <v>10</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>102</v>
@@ -4238,7 +4256,7 @@
         <v>27</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>69</v>
@@ -4247,12 +4265,12 @@
         <v>10</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>103</v>
@@ -4261,7 +4279,7 @@
         <v>27</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>71</v>
@@ -4270,12 +4288,12 @@
         <v>10</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>104</v>
@@ -4284,7 +4302,7 @@
         <v>27</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>73</v>
@@ -4293,12 +4311,12 @@
         <v>10</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>105</v>
@@ -4307,7 +4325,7 @@
         <v>27</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>75</v>
@@ -4316,12 +4334,12 @@
         <v>10</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>106</v>
@@ -4330,7 +4348,7 @@
         <v>27</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>77</v>
@@ -4339,12 +4357,12 @@
         <v>10</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>107</v>
@@ -4353,7 +4371,7 @@
         <v>9</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>108</v>
@@ -4362,12 +4380,12 @@
         <v>10</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>109</v>
@@ -4376,7 +4394,7 @@
         <v>9</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>110</v>
@@ -4385,12 +4403,12 @@
         <v>10</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>111</v>
@@ -4399,7 +4417,7 @@
         <v>9</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>112</v>
@@ -4408,12 +4426,12 @@
         <v>10</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>78</v>
@@ -4422,7 +4440,7 @@
         <v>27</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>79</v>
@@ -4431,12 +4449,12 @@
         <v>10</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>80</v>
@@ -4445,7 +4463,7 @@
         <v>27</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>81</v>
@@ -4454,12 +4472,12 @@
         <v>10</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>82</v>
@@ -4468,7 +4486,7 @@
         <v>27</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>83</v>
@@ -4477,12 +4495,12 @@
         <v>10</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>84</v>
@@ -4491,7 +4509,7 @@
         <v>27</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>85</v>
@@ -4500,12 +4518,12 @@
         <v>10</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>113</v>
@@ -4514,7 +4532,7 @@
         <v>27</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>114</v>
@@ -4523,719 +4541,2260 @@
         <v>10</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>129</v>
+        <v>36</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>131</v>
+        <v>38</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>132</v>
+        <v>39</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>133</v>
+        <v>40</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>136</v>
+        <v>43</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>138</v>
+        <v>45</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>140</v>
+        <v>47</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>141</v>
+        <v>49</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>145</v>
+        <v>51</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>149</v>
+        <v>55</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>151</v>
+        <v>57</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>153</v>
+        <v>59</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>155</v>
+        <v>98</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>160</v>
+        <v>101</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>163</v>
+        <v>69</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>175</v>
+        <v>81</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G209" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G213" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G216" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G217" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F221" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G221" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G222" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G223" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G229" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G233" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G235" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G236" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F237" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G237" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G239" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G241" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G242" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G243" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G244" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G245" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G246" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F247" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G247" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G248" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G249" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G250" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F251" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G251" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F252" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G252" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G253" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F254" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G254" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F255" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G255" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F256" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G256" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G257" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E258" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B201" s="2" t="s">
+      <c r="F258" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G258" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G259" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G260" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F261" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G261" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F262" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G262" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F263" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G263" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F264" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G264" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E265" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C201" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E201" s="2" t="s">
+      <c r="F265" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G265" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B266" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F201" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G201" s="2" t="s">
+      <c r="C266" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F266" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G266" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F267" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G267" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F268" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G268" s="2" t="s">
         <v>18</v>
       </c>
     </row>
